--- a/sampleprojects/CorporateTax/excel/states/NY_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/NY_corp.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>DT: Determine NY Filing Requirement</t>
   </si>
@@ -143,7 +143,7 @@
     <t>Calculate NY tax at 6.5% flat rate; NY uses flat 6.5% rate (Tax Law § 209), subtract credits, calculate refund/owed</t>
   </si>
   <si>
-    <t>set apportionment.state_tax = the maximum of (apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set apportionment.state_tax = the maximum of (apportionment.state_taxable_income * ny_apportionment.state_tax_rate - apportionment.state_credits) and (0.0); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No nexus - no tax liability; No NY nexus - any estimated payments are refunded</t>
@@ -167,7 +167,7 @@
     <t>Business operates in MTA region</t>
   </si>
   <si>
-    <t>result.ny_in_mta_region == true</t>
+    <t>ny_result.in_mta_region == true</t>
   </si>
   <si>
     <t>Has positive tax base for surcharge calculation</t>
@@ -176,13 +176,13 @@
     <t>Calculate MTA surcharge at 0.34%; MTA surcharge is 0.34% of business income base, add to total state tax, recalculate refund/owed</t>
   </si>
   <si>
-    <t>set result.ny_mta_surcharge = apportionment.state_taxable_income * result.ny_mta_surcharge_rate; set apportionment.state_tax = apportionment.state_tax + result.ny_mta_surcharge; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set ny_result.mta_surcharge = apportionment.state_taxable_income * ny_result.mta_surcharge_rate; set apportionment.state_tax = apportionment.state_tax + ny_result.mta_surcharge; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No MTA surcharge - not in MTA region</t>
   </si>
   <si>
-    <t>set result.ny_mta_surcharge = 0.0;</t>
+    <t>set ny_result.mta_surcharge = 0.0;</t>
   </si>
   <si>
     <t>No MTA surcharge - no nexus; No MTA surcharge - no NY nexus or no taxable income</t>
@@ -233,10 +233,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>ny_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -266,82 +266,55 @@
     <t>Economic nexus gross receipts threshold - NY uses $1M threshold</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>NY corporate income tax rate - 6.5% per Tax Law § 209</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Economic nexus transaction count threshold - Default 200 (update if state differs)</t>
+  </si>
+  <si>
+    <t>ny_result</t>
+  </si>
+  <si>
+    <t>(3 attributes)</t>
+  </si>
+  <si>
+    <t>in_mta_region</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>Business located in MTA region (NYC metro area)</t>
+  </si>
+  <si>
+    <t>mta_surcharge</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>State-specific additions: federal interest, IRC 199A addback, bonus depreciation, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>NY</t>
-  </si>
-  <si>
-    <t>Two-letter state code - New York</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>State tax credits: R&amp;D, jobs, film, renewable energy, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>State-specific subtractions: municipal interest, state taxes, state NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>NY corporate income tax rate - 6.5% per Tax Law § 209</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>Economic nexus transaction count threshold - Default 200 (update if state differs)</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(3 attributes)</t>
-  </si>
-  <si>
-    <t>ny_in_mta_region</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>Business located in MTA region (NYC metro area)</t>
-  </si>
-  <si>
-    <t>ny_mta_surcharge</t>
-  </si>
-  <si>
     <t>NY MTA surcharge amount calculated</t>
   </si>
   <si>
-    <t>ny_mta_surcharge_rate</t>
+    <t>mta_surcharge_rate</t>
   </si>
   <si>
     <t>0.0034</t>
@@ -3309,14 +3282,14 @@
       <c r="B7" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>74</v>
+      <c r="C7" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -3325,7 +3298,7 @@
         <v>76</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -3344,308 +3317,144 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="A8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H8" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="H9" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>76</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>76</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="7" t="s">
+      <c r="I11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>14</v>
       </c>
     </row>
